--- a/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,13 +103,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-examination-report</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-examination-report|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-acte-imagerie</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-acte-imagerie|0.1.0</t>
   </si>
   <si>
     <t>FRLMExaminationReport</t>
@@ -151,7 +151,7 @@
     <t>FRCDADICOMActeImagerie.entry.frDICOMAdministrationProduitDeSante</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-conclusion</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-conclusion|0.1.0</t>
   </si>
   <si>
     <t>FRLMExaminationReport.subSection.conclusion</t>
@@ -160,7 +160,7 @@
     <t>FRCDASectionDICOMConclusion</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-resultats</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-resultats|0.1.0</t>
   </si>
   <si>
     <t>FRLMExaminationReport.entry.results[x]</t>
@@ -169,7 +169,7 @@
     <t>FRCDADICOMResultats</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>FRCompositionDocument.section:sectionImpression</t>
@@ -193,7 +193,7 @@
     <t>FRCompositionDocument.section:Findings.entry:FRObservationResultDocument</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-diagnostic-report-imaging-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0</t>
   </si>
   <si>
     <t>FRDiagnosticReportImagingDocument.conclusion</t>

--- a/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRSectionExaminationReportLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -55,10 +58,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,7 +109,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-examination-report|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMExaminationReport|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -118,37 +124,40 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Section</t>
+  </si>
+  <si>
     <t>FRCDADICOMActeImagerie</t>
   </si>
   <si>
     <t>FRLMExaminationReport.codeSection</t>
   </si>
   <si>
-    <t>FRCDADICOMActeImagerie.code</t>
+    <t>Section.code</t>
   </si>
   <si>
     <t>FRLMExaminationReport.titleSection</t>
   </si>
   <si>
-    <t>FRCDADICOMActeImagerie.title</t>
+    <t>Section.title</t>
   </si>
   <si>
     <t>FRLMExaminationReport.description</t>
   </si>
   <si>
-    <t>FRCDADICOMActeImagerie.text</t>
+    <t>Section.text</t>
   </si>
   <si>
     <t>FRLMExaminationReport.entry.imagingProcedures</t>
   </si>
   <si>
-    <t>FRCDADICOMActeImagerie.entry.frDICOMTechniqueImagerie</t>
+    <t>Section.entry:frDicomTechniqueImagerie.procedure</t>
   </si>
   <si>
     <t>FRLMExaminationReport.entry.medicationAdministrations</t>
   </si>
   <si>
-    <t>FRCDADICOMActeImagerie.entry.frDICOMAdministrationProduitDeSante</t>
+    <t>Section.entry:frDicomAdministrationProduitDeSante.substanceAdministration</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-conclusion|0.1.0</t>
@@ -172,40 +181,46 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
+    <t>Composition.section</t>
+  </si>
+  <si>
     <t>FRCompositionDocument.section:sectionImpression</t>
   </si>
   <si>
-    <t>FRCompositionDocument.section:sectionImagingStudy.entry:ImagingStudy.procedureReference:FRProcedureImagingDocument</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sectionImagingStudy.entry:ImagingStudy.procedureReference:FRProcedureImagingDocument.partOf:FRMedicationAdministrationDocument</t>
+    <t>Composition.section.entry</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument</t>
+  </si>
+  <si>
+    <t>FRMedicationAdministrationDocument</t>
   </si>
   <si>
     <t>FRLMExaminationReport.entry.adverseReactions</t>
   </si>
   <si>
-    <t>FRCompositionDocument.section:sectionPredictableAdverseDrugReaction.entry:FRAdverseEventDocument</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:Findings.text</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:Findings.entry:FRObservationResultDocument</t>
+    <t>FRAllergyIntoleranceDocument</t>
+  </si>
+  <si>
+    <t>Composition.section.text</t>
+  </si>
+  <si>
+    <t>Observation</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0</t>
   </si>
   <si>
+    <t>DiagnosticReport.conclusion</t>
+  </si>
+  <si>
     <t>FRDiagnosticReportImagingDocument.conclusion</t>
   </si>
   <si>
-    <t>FRDiagnosticReportImagingDocument.extension:procedure</t>
-  </si>
-  <si>
-    <t>FRDiagnosticReportImagingDocument.extension:procedure.partOf:FRMedicationAdministrationDocument</t>
-  </si>
-  <si>
-    <t>FRDiagnosticReportImagingDocument.result</t>
+    <t>DiagnosticReport.extension:procedure</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result</t>
   </si>
 </sst>
 </file>
@@ -374,79 +389,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -462,113 +481,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -584,50 +605,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -641,50 +664,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -698,115 +723,125 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -820,87 +855,89 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>

--- a/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
